--- a/file/Catalog_Experiences_Web_VPATJ03600.xlsx
+++ b/file/Catalog_Experiences_Web_VPATJ03600.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D78451-69C4-460A-A4CE-F41A32540BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C76B3DE-D230-41C4-B92E-94BB49D9E632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00FD911C-D16F-48DE-9A30-FA5A7C071AE3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6BDCFBF7-A53C-477F-9FB0-3BC33E5182F9}"/>
   </bookViews>
   <sheets>
-    <sheet name="情報アクセシビリティ自己評価様式" sheetId="1" r:id="rId1"/>
-    <sheet name="様式作成時の技術基準" sheetId="2" r:id="rId2"/>
+    <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
+    <sheet name="様式作成時の技術基準" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">様式作成時の技術基準!$A$1:$M$90</definedName>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -55,7 +58,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -65,16 +68,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -84,7 +87,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -93,7 +96,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -103,16 +106,16 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -139,7 +142,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -151,7 +154,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -168,7 +171,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>Catalog Experiences_x000D_
+    <t>Catalog Experiences
 (Web)</t>
   </si>
   <si>
@@ -178,7 +181,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -189,12 +192,13 @@
   </si>
   <si>
     <t>Catalog Experiences(Web)</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -210,7 +214,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -225,7 +229,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
@@ -234,7 +238,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
@@ -242,7 +246,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
@@ -251,7 +255,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
@@ -259,7 +263,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
@@ -272,7 +276,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -289,7 +293,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -300,7 +304,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -312,7 +316,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -377,7 +381,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -389,7 +393,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -453,7 +457,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -469,7 +473,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -479,7 +483,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -488,7 +492,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -579,7 +583,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -595,7 +599,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -686,7 +690,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -699,7 +703,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -753,7 +757,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -810,7 +814,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -822,7 +826,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -832,7 +836,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -841,7 +845,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -855,7 +859,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="11"/>
+        <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
@@ -1620,7 +1624,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1652,19 +1656,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
@@ -1687,18 +1698,26 @@
     </font>
     <font>
       <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
       <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1714,38 +1733,16 @@
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10.5"/>
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="10.5"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -2071,192 +2068,195 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2280,16 +2280,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2626,228 +2626,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05919141-0691-40DB-94F1-8C45632C9609}">
-  <sheetPr codeName="Sheet592">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428CA5AB-75FE-4778-A6B8-58BB6923C1D8}">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="2"/>
-    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="2"/>
+    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="3"/>
+    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="10" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="18"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18"/>
+      <c r="A7" s="14"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
+      <c r="A9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="18"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="18"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
@@ -2965,13 +2965,13 @@
       <c r="D24" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
@@ -2980,11 +2980,11 @@
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
       <c r="D25" s="42"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="45"/>
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
@@ -2995,13 +2995,13 @@
       <c r="D26" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
@@ -3010,11 +3010,11 @@
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
       <c r="D27" s="42"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
@@ -3191,28 +3191,28 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="1:9" ht="18.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
@@ -3262,15 +3262,15 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
@@ -3289,11 +3289,11 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="4"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="5"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
@@ -3311,7 +3311,8 @@
       <c r="H48" s="42"/>
       <c r="I48" s="42"/>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="58"/>
       <c r="B49" s="42"/>
       <c r="C49" s="42"/>
       <c r="D49" s="42"/>
@@ -3321,7 +3322,8 @@
       <c r="H49" s="42"/>
       <c r="I49" s="42"/>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="58"/>
       <c r="B50" s="42"/>
       <c r="C50" s="42"/>
       <c r="D50" s="42"/>
@@ -3331,7 +3333,8 @@
       <c r="H50" s="42"/>
       <c r="I50" s="42"/>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="58"/>
       <c r="B51" s="42"/>
       <c r="C51" s="42"/>
       <c r="D51" s="42"/>
@@ -3341,7 +3344,8 @@
       <c r="H51" s="42"/>
       <c r="I51" s="42"/>
     </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="58"/>
       <c r="B52" s="42"/>
       <c r="C52" s="42"/>
       <c r="D52" s="42"/>
@@ -3351,7 +3355,8 @@
       <c r="H52" s="42"/>
       <c r="I52" s="42"/>
     </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="58"/>
       <c r="B53" s="42"/>
       <c r="C53" s="42"/>
       <c r="D53" s="42"/>
@@ -3361,7 +3366,8 @@
       <c r="H53" s="42"/>
       <c r="I53" s="42"/>
     </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="58"/>
       <c r="B54" s="42"/>
       <c r="C54" s="42"/>
       <c r="D54" s="42"/>
@@ -3439,2252 +3445,2252 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184CB4BB-4498-4401-ADFA-7365FDD0B439}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D155A5FE-C25E-4853-BD44-CEF726E85B7C}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" style="64" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.08203125" style="63" customWidth="1"/>
-    <col min="3" max="3" width="33.08203125" style="63" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.08203125" style="64" customWidth="1"/>
+    <col min="3" max="3" width="33.08203125" style="64" customWidth="1"/>
     <col min="4" max="13" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="59" t="s">
+      <c r="F1" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="59" t="s">
+      <c r="L1" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="60" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="61">
+      <c r="A2" s="62">
         <v>301</v>
       </c>
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="63" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="65" t="s">
+      <c r="D2" s="65"/>
+      <c r="E2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="65" t="s">
+      <c r="G2" s="67"/>
+      <c r="H2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="65" t="s">
+      <c r="I2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="65" t="s">
+      <c r="J2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="65" t="s">
+      <c r="K2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="L2" s="65" t="s">
+      <c r="L2" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="M2" s="65" t="s">
+      <c r="M2" s="66" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="61">
+      <c r="A3" s="62">
         <v>302</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="64" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="64"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="66"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="64">
+      <c r="A4" s="65">
         <v>302.10000000000002</v>
       </c>
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="64" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="65"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="64">
+      <c r="A5" s="65">
         <v>302.2</v>
       </c>
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="67"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="68"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="64">
+      <c r="A6" s="65">
         <v>302.3</v>
       </c>
-      <c r="B6" s="63" t="s">
+      <c r="B6" s="64" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="68"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="65"/>
+      <c r="L6" s="65"/>
+      <c r="M6" s="65"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="64">
+      <c r="A7" s="65">
         <v>302.39999999999998</v>
       </c>
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="65"/>
+      <c r="J7" s="65"/>
+      <c r="K7" s="65"/>
+      <c r="L7" s="65"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="64">
+      <c r="A8" s="65">
         <v>302.5</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="64"/>
-      <c r="K8" s="64"/>
-      <c r="L8" s="64"/>
-      <c r="M8" s="64"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="64">
+      <c r="A9" s="65">
         <v>302.60000000000002</v>
       </c>
-      <c r="B9" s="63" t="s">
+      <c r="B9" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="K9" s="64"/>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="64">
+      <c r="A10" s="65">
         <v>302.7</v>
       </c>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="64"/>
-      <c r="K10" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L10" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M10" s="64"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="65"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="64">
+      <c r="A11" s="65">
         <v>302.8</v>
       </c>
-      <c r="B11" s="63" t="s">
+      <c r="B11" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="64"/>
-      <c r="K11" s="64" t="s">
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65"/>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="L11" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M11" s="64"/>
+      <c r="L11" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M11" s="65"/>
     </row>
     <row r="12" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="64">
+      <c r="A12" s="65">
         <v>302.89999999999998</v>
       </c>
-      <c r="B12" s="63" t="s">
+      <c r="B12" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="64"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="65"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="64">
+      <c r="A13" s="65">
         <v>402</v>
       </c>
-      <c r="B13" s="63" t="s">
+      <c r="B13" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="64"/>
-      <c r="E13" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="66"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-    </row>
-    <row r="14" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="68">
+      <c r="D13" s="65"/>
+      <c r="E13" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="67"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="66"/>
+      <c r="M13" s="66"/>
+    </row>
+    <row r="14" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="69">
         <v>402.1</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="66"/>
+      <c r="M14" s="66"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="64">
+      <c r="A15" s="65">
         <v>402.2</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="64" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="64" t="s">
+      <c r="A16" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="64" t="s">
         <v>94</v>
       </c>
-      <c r="C16" s="63" t="s">
+      <c r="C16" s="64" t="s">
         <v>95</v>
       </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="64"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64"/>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="65"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="64" t="s">
         <v>98</v>
       </c>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="64"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="64"/>
+      <c r="D17" s="65"/>
+      <c r="E17" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="65"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="65" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="64" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="64"/>
-      <c r="K18" s="64"/>
-      <c r="L18" s="64"/>
-      <c r="M18" s="64"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="68"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="65" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="63" t="s">
+      <c r="C19" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F19" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G19" s="67"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="64"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="64"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="68"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="C20" s="63" t="s">
+      <c r="C20" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="D20" s="64"/>
-      <c r="E20" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="64"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="64"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="65"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="64">
+      <c r="A21" s="65">
         <v>402.3</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
+      <c r="D21" s="65"/>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="C22" s="63" t="s">
+      <c r="C22" s="64" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="64"/>
-      <c r="E22" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="64"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="65"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="63" t="s">
+      <c r="C23" s="64" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="64"/>
-      <c r="E23" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="64"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="65"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="65"/>
+      <c r="K23" s="65"/>
+      <c r="L23" s="65"/>
+      <c r="M23" s="65"/>
     </row>
     <row r="24" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="64">
+      <c r="A24" s="65">
         <v>402.4</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="64" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="63" t="s">
+      <c r="C24" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="67"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="64"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="68"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
+      <c r="J24" s="65"/>
+      <c r="K24" s="65"/>
+      <c r="L24" s="65"/>
+      <c r="M24" s="65"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="64">
+      <c r="A25" s="65">
         <v>402.5</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="64" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="64" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="64"/>
-      <c r="F25" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="67"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="64"/>
-      <c r="J25" s="64"/>
-      <c r="K25" s="64"/>
-      <c r="L25" s="64"/>
-      <c r="M25" s="64"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="68"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="64">
+      <c r="A26" s="65">
         <v>403</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="64" t="s">
         <v>120</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="64" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="64"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="K26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L26" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" s="67"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26" s="66"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="64">
+      <c r="A27" s="65">
         <v>403.1</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C27" s="63" t="s">
+      <c r="C27" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="66"/>
+      <c r="F27" s="66"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+      <c r="J27" s="66"/>
+      <c r="K27" s="66"/>
+      <c r="L27" s="66"/>
+      <c r="M27" s="66"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="64">
+      <c r="A28" s="65">
         <v>404</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="64" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="64" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F28" s="65"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J28" s="65"/>
-      <c r="K28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L28" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M28" s="65"/>
+      <c r="D28" s="65"/>
+      <c r="E28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="66"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M28" s="66"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="64">
+      <c r="A29" s="65">
         <v>404.1</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D29" s="64"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="64">
+      <c r="A30" s="65">
         <v>405</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="64" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="63" t="s">
+      <c r="C30" s="64" t="s">
         <v>128</v>
       </c>
-      <c r="D30" s="64"/>
-      <c r="E30" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="65"/>
-      <c r="M30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="64">
+      <c r="A31" s="65">
         <v>405.1</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="63" t="s">
+      <c r="C31" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="64"/>
-      <c r="E31" s="65"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="66"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
-      <c r="K31" s="65"/>
-      <c r="L31" s="65"/>
-      <c r="M31" s="65"/>
+      <c r="D31" s="65"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="66"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="66"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="64">
+      <c r="A32" s="65">
         <v>406</v>
       </c>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="64" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="63" t="s">
+      <c r="C32" s="64" t="s">
         <v>130</v>
       </c>
-      <c r="D32" s="64"/>
-      <c r="E32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F32" s="65"/>
-      <c r="G32" s="66"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L32" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M32" s="65" t="s">
+      <c r="D32" s="65"/>
+      <c r="E32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="66"/>
+      <c r="G32" s="67"/>
+      <c r="H32" s="66"/>
+      <c r="I32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J32" s="66"/>
+      <c r="K32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L32" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="66" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="64">
+      <c r="A33" s="65">
         <v>406.1</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="64"/>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="65"/>
-      <c r="I33" s="65"/>
-      <c r="J33" s="65"/>
-      <c r="K33" s="65"/>
-      <c r="L33" s="65"/>
-      <c r="M33" s="65"/>
+      <c r="D33" s="65"/>
+      <c r="E33" s="66"/>
+      <c r="F33" s="66"/>
+      <c r="G33" s="67"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+      <c r="K33" s="66"/>
+      <c r="L33" s="66"/>
+      <c r="M33" s="66"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="64">
+      <c r="A34" s="65">
         <v>407</v>
       </c>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="64" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="63" t="s">
+      <c r="C34" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="D34" s="64"/>
-      <c r="E34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" s="66"/>
-      <c r="H34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34" s="65"/>
-      <c r="K34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L34" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M34" s="65"/>
+      <c r="D34" s="65"/>
+      <c r="E34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="67"/>
+      <c r="H34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="66"/>
+      <c r="K34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L34" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="66"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="64">
+      <c r="A35" s="65">
         <v>407.1</v>
       </c>
-      <c r="B35" s="63" t="s">
+      <c r="B35" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D35" s="64"/>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="66"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
+      <c r="D35" s="65"/>
+      <c r="E35" s="66"/>
+      <c r="F35" s="66"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="66"/>
+      <c r="I35" s="66"/>
+      <c r="J35" s="66"/>
+      <c r="K35" s="66"/>
+      <c r="L35" s="66"/>
+      <c r="M35" s="66"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="64">
+      <c r="A36" s="65">
         <v>407.2</v>
       </c>
-      <c r="B36" s="63" t="s">
+      <c r="B36" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="63" t="s">
+      <c r="C36" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
-      <c r="F36" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="64"/>
-      <c r="K36" s="64"/>
-      <c r="L36" s="64"/>
-      <c r="M36" s="64"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
+      <c r="F36" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="68"/>
+      <c r="H36" s="65"/>
+      <c r="I36" s="65"/>
+      <c r="J36" s="65"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
     </row>
     <row r="37" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="64">
+      <c r="A37" s="65">
         <v>407.3</v>
       </c>
-      <c r="B37" s="63" t="s">
+      <c r="B37" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F37" s="64"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="64"/>
-      <c r="K37" s="64"/>
-      <c r="L37" s="64"/>
-      <c r="M37" s="64"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="65"/>
+      <c r="G37" s="68"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="64">
+      <c r="A38" s="65">
         <v>407.4</v>
       </c>
-      <c r="B38" s="63" t="s">
+      <c r="B38" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="63" t="s">
+      <c r="C38" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="D38" s="64"/>
-      <c r="E38" s="64"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="64"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L38" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="68"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L38" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M38" s="65"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="64">
+      <c r="A39" s="65">
         <v>407.5</v>
       </c>
-      <c r="B39" s="63" t="s">
+      <c r="B39" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="C39" s="63" t="s">
+      <c r="C39" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="D39" s="64"/>
-      <c r="E39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" s="67"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L39" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M39" s="64"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G39" s="68"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="65"/>
+      <c r="J39" s="65"/>
+      <c r="K39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L39" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="65"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="64">
+      <c r="A40" s="65">
         <v>407.6</v>
       </c>
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="C40" s="63" t="s">
+      <c r="C40" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="64"/>
-      <c r="E40" s="64"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="64"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L40" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M40" s="64"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="65"/>
+      <c r="F40" s="65"/>
+      <c r="G40" s="68"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="65"/>
+      <c r="J40" s="65"/>
+      <c r="K40" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M40" s="65"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="64">
+      <c r="A41" s="65">
         <v>407.7</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="B41" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="64" t="s">
         <v>144</v>
       </c>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F41" s="64"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="64"/>
-      <c r="J41" s="64"/>
-      <c r="K41" s="64"/>
-      <c r="L41" s="64"/>
-      <c r="M41" s="64"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="65"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="65"/>
+      <c r="J41" s="65"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="65"/>
+      <c r="M41" s="65"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="64">
+      <c r="A42" s="65">
         <v>407.8</v>
       </c>
-      <c r="B42" s="63" t="s">
+      <c r="B42" s="64" t="s">
         <v>145</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="64" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="64"/>
-      <c r="E42" s="64"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="64"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L42" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M42" s="64"/>
+      <c r="D42" s="65"/>
+      <c r="E42" s="65"/>
+      <c r="F42" s="65"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="65"/>
+      <c r="J42" s="65"/>
+      <c r="K42" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L42" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="65"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="64">
+      <c r="A43" s="65">
         <v>408</v>
       </c>
-      <c r="B43" s="63" t="s">
+      <c r="B43" s="64" t="s">
         <v>147</v>
       </c>
-      <c r="C43" s="63" t="s">
+      <c r="C43" s="64" t="s">
         <v>148</v>
       </c>
-      <c r="D43" s="65"/>
-      <c r="E43" s="65"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="65"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="65"/>
-      <c r="K43" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L43" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M43" s="65"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+      <c r="K43" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L43" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="66"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="64">
+      <c r="A44" s="65">
         <v>408.1</v>
       </c>
-      <c r="B44" s="63" t="s">
+      <c r="B44" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="63" t="s">
+      <c r="C44" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D44" s="65"/>
-      <c r="E44" s="65"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="66"/>
-      <c r="H44" s="65"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="65"/>
-      <c r="K44" s="65"/>
-      <c r="L44" s="65"/>
-      <c r="M44" s="65"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="66"/>
+      <c r="J44" s="66"/>
+      <c r="K44" s="66"/>
+      <c r="L44" s="66"/>
+      <c r="M44" s="66"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="64">
+      <c r="A45" s="65">
         <v>408.2</v>
       </c>
-      <c r="B45" s="63" t="s">
+      <c r="B45" s="64" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="64" t="s">
         <v>150</v>
       </c>
-      <c r="D45" s="65"/>
-      <c r="E45" s="65"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="65"/>
-      <c r="I45" s="65"/>
-      <c r="J45" s="65"/>
-      <c r="K45" s="65"/>
-      <c r="L45" s="65"/>
-      <c r="M45" s="65"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="66"/>
+      <c r="K45" s="66"/>
+      <c r="L45" s="66"/>
+      <c r="M45" s="66"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="64">
+      <c r="A46" s="65">
         <v>408.3</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="64" t="s">
         <v>151</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="D46" s="64"/>
-      <c r="E46" s="64"/>
-      <c r="F46" s="64"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="64"/>
-      <c r="I46" s="64"/>
-      <c r="J46" s="64"/>
-      <c r="K46" s="64"/>
-      <c r="L46" s="64"/>
-      <c r="M46" s="64"/>
+      <c r="D46" s="65"/>
+      <c r="E46" s="65"/>
+      <c r="F46" s="65"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="65"/>
+      <c r="I46" s="65"/>
+      <c r="J46" s="65"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="65"/>
+      <c r="M46" s="65"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="64">
+      <c r="A47" s="65">
         <v>409</v>
       </c>
-      <c r="B47" s="63" t="s">
+      <c r="B47" s="64" t="s">
         <v>153</v>
       </c>
-      <c r="C47" s="63" t="s">
+      <c r="C47" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="D47" s="64"/>
-      <c r="E47" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F47" s="65"/>
-      <c r="G47" s="66"/>
-      <c r="H47" s="65"/>
-      <c r="I47" s="65"/>
-      <c r="J47" s="65"/>
-      <c r="K47" s="65"/>
-      <c r="L47" s="65"/>
-      <c r="M47" s="65"/>
+      <c r="D47" s="65"/>
+      <c r="E47" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" s="66"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+      <c r="K47" s="66"/>
+      <c r="L47" s="66"/>
+      <c r="M47" s="66"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="64">
+      <c r="A48" s="65">
         <v>409.1</v>
       </c>
-      <c r="B48" s="63" t="s">
+      <c r="B48" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="63" t="s">
+      <c r="C48" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D48" s="64"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="65"/>
-      <c r="L48" s="65"/>
-      <c r="M48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
+      <c r="K48" s="66"/>
+      <c r="L48" s="66"/>
+      <c r="M48" s="66"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="64">
+      <c r="A49" s="65">
         <v>410</v>
       </c>
-      <c r="B49" s="63" t="s">
+      <c r="B49" s="64" t="s">
         <v>155</v>
       </c>
-      <c r="C49" s="63" t="s">
+      <c r="C49" s="64" t="s">
         <v>156</v>
       </c>
-      <c r="D49" s="64"/>
-      <c r="E49" s="65"/>
-      <c r="F49" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G49" s="66"/>
-      <c r="H49" s="65"/>
-      <c r="I49" s="65"/>
-      <c r="J49" s="65"/>
-      <c r="K49" s="65"/>
-      <c r="L49" s="65"/>
-      <c r="M49" s="65"/>
+      <c r="D49" s="65"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G49" s="67"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+      <c r="K49" s="66"/>
+      <c r="L49" s="66"/>
+      <c r="M49" s="66"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="64">
+      <c r="A50" s="65">
         <v>410.1</v>
       </c>
-      <c r="B50" s="63" t="s">
+      <c r="B50" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="63" t="s">
+      <c r="C50" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D50" s="64"/>
-      <c r="E50" s="65"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
-      <c r="J50" s="65"/>
-      <c r="K50" s="65"/>
-      <c r="L50" s="65"/>
-      <c r="M50" s="65"/>
+      <c r="D50" s="65"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="66"/>
+      <c r="K50" s="66"/>
+      <c r="L50" s="66"/>
+      <c r="M50" s="66"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="64">
+      <c r="A51" s="65">
         <v>411</v>
       </c>
-      <c r="B51" s="63" t="s">
+      <c r="B51" s="64" t="s">
         <v>157</v>
       </c>
-      <c r="C51" s="63" t="s">
+      <c r="C51" s="64" t="s">
         <v>158</v>
       </c>
-      <c r="D51" s="64"/>
-      <c r="E51" s="65"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="66"/>
-      <c r="H51" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I51" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J51" s="65"/>
-      <c r="K51" s="65"/>
-      <c r="L51" s="65"/>
-      <c r="M51" s="65"/>
+      <c r="D51" s="65"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I51" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J51" s="66"/>
+      <c r="K51" s="66"/>
+      <c r="L51" s="66"/>
+      <c r="M51" s="66"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="64">
+      <c r="A52" s="65">
         <v>411.1</v>
       </c>
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="63" t="s">
+      <c r="C52" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D52" s="64"/>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="65"/>
-      <c r="L52" s="65"/>
-      <c r="M52" s="65"/>
+      <c r="D52" s="65"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="66"/>
+      <c r="J52" s="66"/>
+      <c r="K52" s="66"/>
+      <c r="L52" s="66"/>
+      <c r="M52" s="66"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="64">
+      <c r="A53" s="65">
         <v>412</v>
       </c>
-      <c r="B53" s="63" t="s">
+      <c r="B53" s="64" t="s">
         <v>159</v>
       </c>
-      <c r="C53" s="63" t="s">
+      <c r="C53" s="64" t="s">
         <v>160</v>
       </c>
-      <c r="D53" s="64"/>
-      <c r="E53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F53" s="65"/>
-      <c r="G53" s="66"/>
-      <c r="H53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J53" s="65"/>
-      <c r="K53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L53" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M53" s="65"/>
+      <c r="D53" s="65"/>
+      <c r="E53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" s="66"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J53" s="66"/>
+      <c r="K53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L53" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M53" s="66"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="64">
+      <c r="A54" s="65">
         <v>412.1</v>
       </c>
-      <c r="B54" s="63" t="s">
+      <c r="B54" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D54" s="64"/>
-      <c r="E54" s="65"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="65"/>
-      <c r="I54" s="65"/>
-      <c r="J54" s="65"/>
-      <c r="K54" s="65"/>
-      <c r="L54" s="65"/>
-      <c r="M54" s="65"/>
+      <c r="D54" s="65"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="67"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="66"/>
+      <c r="J54" s="66"/>
+      <c r="K54" s="66"/>
+      <c r="L54" s="66"/>
+      <c r="M54" s="66"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="64">
+      <c r="A55" s="65">
         <v>412.2</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="64" t="s">
         <v>161</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="D55" s="64"/>
-      <c r="E55" s="64"/>
-      <c r="F55" s="64"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J55" s="64"/>
-      <c r="K55" s="64"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="64"/>
+      <c r="D55" s="65"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="68"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J55" s="65"/>
+      <c r="K55" s="65"/>
+      <c r="L55" s="65"/>
+      <c r="M55" s="65"/>
     </row>
     <row r="56" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="64">
+      <c r="A56" s="65">
         <v>412.3</v>
       </c>
-      <c r="B56" s="63" t="s">
+      <c r="B56" s="64" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="63" t="s">
+      <c r="C56" s="64" t="s">
         <v>164</v>
       </c>
-      <c r="D56" s="64"/>
-      <c r="E56" s="64"/>
-      <c r="F56" s="64"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J56" s="64"/>
-      <c r="K56" s="64"/>
-      <c r="L56" s="64"/>
-      <c r="M56" s="64"/>
+      <c r="D56" s="65"/>
+      <c r="E56" s="65"/>
+      <c r="F56" s="65"/>
+      <c r="G56" s="68"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J56" s="65"/>
+      <c r="K56" s="65"/>
+      <c r="L56" s="65"/>
+      <c r="M56" s="65"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="64">
+      <c r="A57" s="65">
         <v>412.4</v>
       </c>
-      <c r="B57" s="63" t="s">
+      <c r="B57" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="63" t="s">
+      <c r="C57" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="D57" s="64"/>
-      <c r="E57" s="64"/>
-      <c r="F57" s="64"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J57" s="64"/>
-      <c r="K57" s="64"/>
-      <c r="L57" s="64"/>
-      <c r="M57" s="64"/>
+      <c r="D57" s="65"/>
+      <c r="E57" s="65"/>
+      <c r="F57" s="65"/>
+      <c r="G57" s="68"/>
+      <c r="H57" s="65"/>
+      <c r="I57" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J57" s="65"/>
+      <c r="K57" s="65"/>
+      <c r="L57" s="65"/>
+      <c r="M57" s="65"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="64">
+      <c r="A58" s="65">
         <v>412.5</v>
       </c>
-      <c r="B58" s="63" t="s">
+      <c r="B58" s="64" t="s">
         <v>167</v>
       </c>
-      <c r="C58" s="63" t="s">
+      <c r="C58" s="64" t="s">
         <v>168</v>
       </c>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="64"/>
-      <c r="G58" s="67"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="64"/>
-      <c r="J58" s="64"/>
-      <c r="K58" s="64"/>
-      <c r="L58" s="64"/>
-      <c r="M58" s="64"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="68"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="64">
+      <c r="A59" s="65">
         <v>412.6</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B59" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="C59" s="63" t="s">
+      <c r="C59" s="64" t="s">
         <v>170</v>
       </c>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G59" s="67"/>
-      <c r="H59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I59" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J59" s="64"/>
-      <c r="K59" s="64"/>
-      <c r="L59" s="64"/>
-      <c r="M59" s="64"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G59" s="68"/>
+      <c r="H59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J59" s="65"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="64">
+      <c r="A60" s="65">
         <v>412.7</v>
       </c>
-      <c r="B60" s="63" t="s">
+      <c r="B60" s="64" t="s">
         <v>171</v>
       </c>
-      <c r="C60" s="63" t="s">
+      <c r="C60" s="64" t="s">
         <v>172</v>
       </c>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="64"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I60" s="64"/>
-      <c r="J60" s="64"/>
-      <c r="K60" s="64"/>
-      <c r="L60" s="64"/>
-      <c r="M60" s="64"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="65"/>
+      <c r="G60" s="68"/>
+      <c r="H60" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" s="65"/>
+      <c r="J60" s="65"/>
+      <c r="K60" s="65"/>
+      <c r="L60" s="65"/>
+      <c r="M60" s="65"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="64">
+      <c r="A61" s="65">
         <v>413</v>
       </c>
-      <c r="B61" s="63" t="s">
+      <c r="B61" s="64" t="s">
         <v>173</v>
       </c>
-      <c r="C61" s="63" t="s">
+      <c r="C61" s="64" t="s">
         <v>174</v>
       </c>
-      <c r="D61" s="64"/>
-      <c r="E61" s="65"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I61" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J61" s="65"/>
-      <c r="K61" s="65"/>
-      <c r="L61" s="65"/>
-      <c r="M61" s="65"/>
+      <c r="D61" s="65"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="67"/>
+      <c r="H61" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I61" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J61" s="66"/>
+      <c r="K61" s="66"/>
+      <c r="L61" s="66"/>
+      <c r="M61" s="66"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="64">
+      <c r="A62" s="65">
         <v>411.1</v>
       </c>
-      <c r="B62" s="63" t="s">
+      <c r="B62" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="C62" s="63" t="s">
+      <c r="C62" s="64" t="s">
         <v>176</v>
       </c>
-      <c r="D62" s="64"/>
-      <c r="E62" s="65"/>
-      <c r="F62" s="65"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="65"/>
-      <c r="I62" s="65"/>
-      <c r="J62" s="65"/>
-      <c r="K62" s="65"/>
-      <c r="L62" s="65"/>
-      <c r="M62" s="65"/>
+      <c r="D62" s="65"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="67"/>
+      <c r="H62" s="66"/>
+      <c r="I62" s="66"/>
+      <c r="J62" s="66"/>
+      <c r="K62" s="66"/>
+      <c r="L62" s="66"/>
+      <c r="M62" s="66"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="64">
+      <c r="A63" s="65">
         <v>414</v>
       </c>
-      <c r="B63" s="63" t="s">
+      <c r="B63" s="64" t="s">
         <v>177</v>
       </c>
-      <c r="C63" s="63" t="s">
+      <c r="C63" s="64" t="s">
         <v>178</v>
       </c>
-      <c r="D63" s="64"/>
-      <c r="E63" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F63" s="65"/>
-      <c r="G63" s="66"/>
-      <c r="H63" s="65"/>
-      <c r="I63" s="65"/>
-      <c r="J63" s="65"/>
-      <c r="K63" s="65"/>
-      <c r="L63" s="65"/>
-      <c r="M63" s="65"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="66"/>
+      <c r="G63" s="67"/>
+      <c r="H63" s="66"/>
+      <c r="I63" s="66"/>
+      <c r="J63" s="66"/>
+      <c r="K63" s="66"/>
+      <c r="L63" s="66"/>
+      <c r="M63" s="66"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="64">
+      <c r="A64" s="65">
         <v>412.1</v>
       </c>
-      <c r="B64" s="63" t="s">
+      <c r="B64" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="C64" s="63" t="s">
+      <c r="C64" s="64" t="s">
         <v>179</v>
       </c>
-      <c r="D64" s="64"/>
-      <c r="E64" s="65"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="65"/>
-      <c r="I64" s="65"/>
-      <c r="J64" s="65"/>
-      <c r="K64" s="65"/>
-      <c r="L64" s="65"/>
-      <c r="M64" s="65"/>
+      <c r="D64" s="65"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="66"/>
+      <c r="I64" s="66"/>
+      <c r="J64" s="66"/>
+      <c r="K64" s="66"/>
+      <c r="L64" s="66"/>
+      <c r="M64" s="66"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A65" s="64">
+      <c r="A65" s="65">
         <v>415</v>
       </c>
-      <c r="B65" s="63" t="s">
+      <c r="B65" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="C65" s="63" t="s">
+      <c r="C65" s="64" t="s">
         <v>181</v>
       </c>
-      <c r="D65" s="64"/>
-      <c r="E65" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F65" s="65"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I65" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J65" s="65"/>
-      <c r="K65" s="65"/>
-      <c r="L65" s="65"/>
-      <c r="M65" s="65"/>
+      <c r="D65" s="65"/>
+      <c r="E65" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" s="66"/>
+      <c r="G65" s="67"/>
+      <c r="H65" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I65" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J65" s="66"/>
+      <c r="K65" s="66"/>
+      <c r="L65" s="66"/>
+      <c r="M65" s="66"/>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="64">
+      <c r="A66" s="65">
         <v>413.1</v>
       </c>
-      <c r="B66" s="63" t="s">
+      <c r="B66" s="64" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="63" t="s">
+      <c r="C66" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="D66" s="64"/>
-      <c r="E66" s="65"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="66"/>
-      <c r="H66" s="65"/>
-      <c r="I66" s="65"/>
-      <c r="J66" s="65"/>
-      <c r="K66" s="65"/>
-      <c r="L66" s="65"/>
-      <c r="M66" s="65"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="67"/>
+      <c r="H66" s="66"/>
+      <c r="I66" s="66"/>
+      <c r="J66" s="66"/>
+      <c r="K66" s="66"/>
+      <c r="L66" s="66"/>
+      <c r="M66" s="66"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="64">
+      <c r="A67" s="65">
         <v>502</v>
       </c>
-      <c r="B67" s="63" t="s">
+      <c r="B67" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="C67" s="63" t="s">
+      <c r="C67" s="64" t="s">
         <v>185</v>
       </c>
-      <c r="D67" s="64"/>
-      <c r="E67" s="65" t="s">
+      <c r="D67" s="65"/>
+      <c r="E67" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="F67" s="65" t="s">
+      <c r="F67" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="G67" s="66"/>
-      <c r="H67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J67" s="65"/>
-      <c r="K67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L67" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M67" s="65"/>
+      <c r="G67" s="67"/>
+      <c r="H67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J67" s="66"/>
+      <c r="K67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L67" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M67" s="66"/>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A68" s="64">
+      <c r="A68" s="65">
         <v>502.1</v>
       </c>
-      <c r="B68" s="63" t="s">
+      <c r="B68" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="C68" s="63" t="s">
+      <c r="C68" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D68" s="64"/>
-      <c r="E68" s="65"/>
-      <c r="F68" s="65"/>
-      <c r="G68" s="66"/>
-      <c r="H68" s="65"/>
-      <c r="I68" s="65"/>
-      <c r="J68" s="65"/>
-      <c r="K68" s="65"/>
-      <c r="L68" s="65"/>
-      <c r="M68" s="65"/>
+      <c r="D68" s="65"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="67"/>
+      <c r="H68" s="66"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="66"/>
+      <c r="K68" s="66"/>
+      <c r="L68" s="66"/>
+      <c r="M68" s="66"/>
     </row>
     <row r="69" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="64">
+      <c r="A69" s="65">
         <v>502.2</v>
       </c>
-      <c r="B69" s="63" t="s">
+      <c r="B69" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="C69" s="63" t="s">
+      <c r="C69" s="64" t="s">
         <v>187</v>
       </c>
-      <c r="D69" s="64"/>
-      <c r="E69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F69" s="64"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J69" s="64"/>
-      <c r="K69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L69" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M69" s="64"/>
+      <c r="D69" s="65"/>
+      <c r="E69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" s="65"/>
+      <c r="G69" s="68"/>
+      <c r="H69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J69" s="65"/>
+      <c r="K69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L69" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M69" s="65"/>
     </row>
     <row r="70" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="64">
+      <c r="A70" s="65">
         <v>502.3</v>
       </c>
-      <c r="B70" s="63" t="s">
+      <c r="B70" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="C70" s="63" t="s">
+      <c r="C70" s="64" t="s">
         <v>188</v>
       </c>
-      <c r="D70" s="64"/>
-      <c r="E70" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F70" s="64"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="64"/>
-      <c r="J70" s="64"/>
-      <c r="K70" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L70" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M70" s="64"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F70" s="65"/>
+      <c r="G70" s="68"/>
+      <c r="H70" s="65"/>
+      <c r="I70" s="65"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L70" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M70" s="65"/>
     </row>
     <row r="71" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A71" s="64">
+      <c r="A71" s="65">
         <v>502.4</v>
       </c>
-      <c r="B71" s="63" t="s">
+      <c r="B71" s="64" t="s">
         <v>189</v>
       </c>
-      <c r="C71" s="63" t="s">
+      <c r="C71" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="D71" s="64"/>
-      <c r="E71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G71" s="67"/>
-      <c r="H71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J71" s="64"/>
-      <c r="K71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L71" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M71" s="64"/>
+      <c r="D71" s="65"/>
+      <c r="E71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G71" s="68"/>
+      <c r="H71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J71" s="65"/>
+      <c r="K71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L71" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A72" s="64" t="s">
+      <c r="A72" s="65" t="s">
         <v>191</v>
       </c>
-      <c r="B72" s="63" t="s">
+      <c r="B72" s="64" t="s">
         <v>192</v>
       </c>
-      <c r="C72" s="63" t="s">
+      <c r="C72" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="D72" s="64"/>
-      <c r="E72" s="64"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="64"/>
-      <c r="J72" s="64"/>
-      <c r="K72" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L72" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M72" s="64"/>
+      <c r="D72" s="65"/>
+      <c r="E72" s="65"/>
+      <c r="F72" s="65"/>
+      <c r="G72" s="68"/>
+      <c r="H72" s="65"/>
+      <c r="I72" s="65"/>
+      <c r="J72" s="65"/>
+      <c r="K72" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L72" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A73" s="64" t="s">
+      <c r="A73" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="B73" s="63" t="s">
+      <c r="B73" s="64" t="s">
         <v>195</v>
       </c>
-      <c r="C73" s="63" t="s">
+      <c r="C73" s="64" t="s">
         <v>196</v>
       </c>
-      <c r="D73" s="64"/>
-      <c r="E73" s="64"/>
-      <c r="F73" s="64"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="64"/>
-      <c r="J73" s="64"/>
-      <c r="K73" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L73" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M73" s="64"/>
+      <c r="D73" s="65"/>
+      <c r="E73" s="65"/>
+      <c r="F73" s="65"/>
+      <c r="G73" s="68"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="65"/>
+      <c r="K73" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L73" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A74" s="64" t="s">
+      <c r="A74" s="65" t="s">
         <v>197</v>
       </c>
-      <c r="B74" s="63" t="s">
+      <c r="B74" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="C74" s="63" t="s">
+      <c r="C74" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="D74" s="64"/>
-      <c r="E74" s="64"/>
-      <c r="F74" s="64"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="64"/>
-      <c r="I74" s="64"/>
-      <c r="J74" s="64"/>
-      <c r="K74" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L74" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M74" s="64"/>
+      <c r="D74" s="65"/>
+      <c r="E74" s="65"/>
+      <c r="F74" s="65"/>
+      <c r="G74" s="68"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="65"/>
+      <c r="K74" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L74" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A75" s="64" t="s">
+      <c r="A75" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="64" t="s">
         <v>201</v>
       </c>
-      <c r="C75" s="63" t="s">
+      <c r="C75" s="64" t="s">
         <v>202</v>
       </c>
-      <c r="D75" s="64"/>
-      <c r="E75" s="64"/>
-      <c r="F75" s="64"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I75" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J75" s="64"/>
-      <c r="K75" s="64"/>
-      <c r="L75" s="64"/>
-      <c r="M75" s="64"/>
+      <c r="D75" s="65"/>
+      <c r="E75" s="65"/>
+      <c r="F75" s="65"/>
+      <c r="G75" s="68"/>
+      <c r="H75" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I75" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J75" s="65"/>
+      <c r="K75" s="65"/>
+      <c r="L75" s="65"/>
+      <c r="M75" s="65"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A76" s="64" t="s">
+      <c r="A76" s="65" t="s">
         <v>203</v>
       </c>
-      <c r="B76" s="63" t="s">
+      <c r="B76" s="64" t="s">
         <v>204</v>
       </c>
-      <c r="C76" s="63" t="s">
+      <c r="C76" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="64"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G76" s="67"/>
-      <c r="H76" s="64"/>
-      <c r="I76" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J76" s="64"/>
-      <c r="K76" s="64"/>
-      <c r="L76" s="64"/>
-      <c r="M76" s="64"/>
+      <c r="D76" s="65"/>
+      <c r="E76" s="65"/>
+      <c r="F76" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G76" s="68"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J76" s="65"/>
+      <c r="K76" s="65"/>
+      <c r="L76" s="65"/>
+      <c r="M76" s="65"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A77" s="64" t="s">
+      <c r="A77" s="65" t="s">
         <v>206</v>
       </c>
-      <c r="B77" s="63" t="s">
+      <c r="B77" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="63" t="s">
+      <c r="C77" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="D77" s="64"/>
-      <c r="E77" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F77" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G77" s="67"/>
-      <c r="H77" s="64"/>
-      <c r="I77" s="64"/>
-      <c r="J77" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="K77" s="64"/>
-      <c r="L77" s="64"/>
-      <c r="M77" s="64"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F77" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G77" s="68"/>
+      <c r="H77" s="65"/>
+      <c r="I77" s="65"/>
+      <c r="J77" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="K77" s="65"/>
+      <c r="L77" s="65"/>
+      <c r="M77" s="65"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A78" s="64" t="s">
+      <c r="A78" s="65" t="s">
         <v>209</v>
       </c>
-      <c r="B78" s="63" t="s">
+      <c r="B78" s="64" t="s">
         <v>210</v>
       </c>
-      <c r="C78" s="63" t="s">
+      <c r="C78" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="64"/>
-      <c r="E78" s="64"/>
-      <c r="F78" s="64"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I78" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J78" s="64"/>
-      <c r="K78" s="64"/>
-      <c r="L78" s="64"/>
-      <c r="M78" s="64"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="65"/>
+      <c r="F78" s="65"/>
+      <c r="G78" s="68"/>
+      <c r="H78" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I78" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J78" s="65"/>
+      <c r="K78" s="65"/>
+      <c r="L78" s="65"/>
+      <c r="M78" s="65"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A79" s="64">
+      <c r="A79" s="65">
         <v>503</v>
       </c>
-      <c r="B79" s="63" t="s">
+      <c r="B79" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="C79" s="63" t="s">
+      <c r="C79" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="D79" s="64"/>
-      <c r="E79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G79" s="66"/>
-      <c r="H79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J79" s="65"/>
-      <c r="K79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="L79" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="M79" s="65"/>
+      <c r="D79" s="65"/>
+      <c r="E79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G79" s="67"/>
+      <c r="H79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J79" s="66"/>
+      <c r="K79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="L79" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="M79" s="66"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A80" s="64">
+      <c r="A80" s="65">
         <v>503.1</v>
       </c>
-      <c r="B80" s="63" t="s">
+      <c r="B80" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C80" s="63" t="s">
+      <c r="C80" s="64" t="s">
         <v>123</v>
       </c>
-      <c r="D80" s="64"/>
-      <c r="E80" s="65"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="65"/>
-      <c r="I80" s="65"/>
-      <c r="J80" s="65"/>
-      <c r="K80" s="65"/>
-      <c r="L80" s="65"/>
-      <c r="M80" s="65"/>
+      <c r="D80" s="65"/>
+      <c r="E80" s="66"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="67"/>
+      <c r="H80" s="66"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="66"/>
+      <c r="K80" s="66"/>
+      <c r="L80" s="66"/>
+      <c r="M80" s="66"/>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A81" s="64">
+      <c r="A81" s="65">
         <v>503.2</v>
       </c>
-      <c r="B81" s="63" t="s">
+      <c r="B81" s="64" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="63" t="s">
+      <c r="C81" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="D81" s="64"/>
-      <c r="E81" s="64"/>
-      <c r="F81" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G81" s="67"/>
-      <c r="H81" s="64"/>
-      <c r="I81" s="64"/>
-      <c r="J81" s="64"/>
-      <c r="K81" s="64"/>
-      <c r="L81" s="64"/>
-      <c r="M81" s="64"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G81" s="68"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="65"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="64">
+      <c r="A82" s="65">
         <v>503.3</v>
       </c>
-      <c r="B82" s="63" t="s">
+      <c r="B82" s="64" t="s">
         <v>216</v>
       </c>
-      <c r="C82" s="63" t="s">
+      <c r="C82" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="D82" s="64"/>
-      <c r="E82" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F82" s="64"/>
-      <c r="G82" s="67"/>
-      <c r="H82" s="64"/>
-      <c r="I82" s="64"/>
-      <c r="J82" s="64"/>
-      <c r="K82" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="L82" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="M82" s="64"/>
+      <c r="D82" s="65"/>
+      <c r="E82" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F82" s="65"/>
+      <c r="G82" s="68"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="65"/>
+      <c r="J82" s="65"/>
+      <c r="K82" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="L82" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="M82" s="65"/>
     </row>
     <row r="83" spans="1:13" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A83" s="64">
+      <c r="A83" s="65">
         <v>503.4</v>
       </c>
-      <c r="B83" s="63" t="s">
+      <c r="B83" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="C83" s="63" t="s">
+      <c r="C83" s="64" t="s">
         <v>219</v>
       </c>
-      <c r="D83" s="64"/>
-      <c r="E83" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F83" s="64"/>
-      <c r="G83" s="67"/>
-      <c r="H83" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I83" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J83" s="64"/>
-      <c r="K83" s="64"/>
-      <c r="L83" s="64"/>
-      <c r="M83" s="64"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F83" s="65"/>
+      <c r="G83" s="68"/>
+      <c r="H83" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I83" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J83" s="65"/>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="64">
+      <c r="A84" s="65">
         <v>504</v>
       </c>
-      <c r="B84" s="63" t="s">
+      <c r="B84" s="64" t="s">
         <v>220</v>
       </c>
-      <c r="C84" s="63" t="s">
+      <c r="C84" s="64" t="s">
         <v>221</v>
       </c>
-      <c r="D84" s="64"/>
-      <c r="E84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="F84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="G84" s="66"/>
-      <c r="H84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="I84" s="65" t="s">
-        <v>72</v>
-      </c>
-      <c r="J84" s="65"/>
-      <c r="K84" s="65"/>
-      <c r="L84" s="65"/>
-      <c r="M84" s="65"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="F84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="G84" s="67"/>
+      <c r="H84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="I84" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="J84" s="66"/>
+      <c r="K84" s="66"/>
+      <c r="L84" s="66"/>
+      <c r="M84" s="66"/>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="64">
+      <c r="A85" s="65">
         <v>504.1</v>
       </c>
-      <c r="B85" s="63" t="s">
+      <c r="B85" s="64" t="s">
         <v>122</v>
       </c>
-      <c r="C85" s="63" t="s">
+      <c r="C85" s="64" t="s">
         <v>126</v>
       </c>
-      <c r="D85" s="64"/>
-      <c r="E85" s="65"/>
-      <c r="F85" s="65"/>
-      <c r="G85" s="66"/>
-      <c r="H85" s="65"/>
-      <c r="I85" s="65"/>
-      <c r="J85" s="65"/>
-      <c r="K85" s="65"/>
-      <c r="L85" s="65"/>
-      <c r="M85" s="65"/>
+      <c r="D85" s="65"/>
+      <c r="E85" s="66"/>
+      <c r="F85" s="66"/>
+      <c r="G85" s="67"/>
+      <c r="H85" s="66"/>
+      <c r="I85" s="66"/>
+      <c r="J85" s="66"/>
+      <c r="K85" s="66"/>
+      <c r="L85" s="66"/>
+      <c r="M85" s="66"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A86" s="64">
+      <c r="A86" s="65">
         <v>504.2</v>
       </c>
-      <c r="B86" s="63" t="s">
+      <c r="B86" s="64" t="s">
         <v>222</v>
       </c>
-      <c r="C86" s="63" t="s">
+      <c r="C86" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="D86" s="64"/>
-      <c r="E86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G86" s="67"/>
-      <c r="H86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I86" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J86" s="64"/>
-      <c r="K86" s="64"/>
-      <c r="L86" s="64"/>
-      <c r="M86" s="64"/>
+      <c r="D86" s="65"/>
+      <c r="E86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G86" s="68"/>
+      <c r="H86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I86" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J86" s="65"/>
+      <c r="K86" s="65"/>
+      <c r="L86" s="65"/>
+      <c r="M86" s="65"/>
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A87" s="64" t="s">
+      <c r="A87" s="65" t="s">
         <v>224</v>
       </c>
-      <c r="B87" s="63" t="s">
+      <c r="B87" s="64" t="s">
         <v>225</v>
       </c>
-      <c r="C87" s="63" t="s">
+      <c r="C87" s="64" t="s">
         <v>226</v>
       </c>
-      <c r="D87" s="64"/>
-      <c r="E87" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F87" s="64"/>
-      <c r="G87" s="67"/>
-      <c r="H87" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I87" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J87" s="64"/>
-      <c r="K87" s="64"/>
-      <c r="L87" s="64"/>
-      <c r="M87" s="64"/>
+      <c r="D87" s="65"/>
+      <c r="E87" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F87" s="65"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J87" s="65"/>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A88" s="64" t="s">
+      <c r="A88" s="65" t="s">
         <v>227</v>
       </c>
-      <c r="B88" s="63" t="s">
+      <c r="B88" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="C88" s="63" t="s">
+      <c r="C88" s="64" t="s">
         <v>229</v>
       </c>
-      <c r="D88" s="64"/>
-      <c r="E88" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F88" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G88" s="67"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="64"/>
-      <c r="J88" s="64"/>
-      <c r="K88" s="64"/>
-      <c r="L88" s="64"/>
-      <c r="M88" s="64"/>
+      <c r="D88" s="65"/>
+      <c r="E88" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F88" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G88" s="68"/>
+      <c r="H88" s="65"/>
+      <c r="I88" s="65"/>
+      <c r="J88" s="65"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
+      <c r="M88" s="65"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A89" s="64">
+      <c r="A89" s="65">
         <v>504.3</v>
       </c>
-      <c r="B89" s="63" t="s">
+      <c r="B89" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="C89" s="63" t="s">
+      <c r="C89" s="64" t="s">
         <v>231</v>
       </c>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G89" s="67"/>
-      <c r="H89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I89" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J89" s="64"/>
-      <c r="K89" s="64"/>
-      <c r="L89" s="64"/>
-      <c r="M89" s="64"/>
+      <c r="D89" s="65"/>
+      <c r="E89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G89" s="68"/>
+      <c r="H89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I89" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J89" s="65"/>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
+      <c r="M89" s="65"/>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="A90" s="64">
+      <c r="A90" s="65">
         <v>504.4</v>
       </c>
-      <c r="B90" s="63" t="s">
+      <c r="B90" s="64" t="s">
         <v>232</v>
       </c>
-      <c r="C90" s="63" t="s">
+      <c r="C90" s="64" t="s">
         <v>233</v>
       </c>
-      <c r="D90" s="64"/>
-      <c r="E90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="F90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G90" s="67"/>
-      <c r="H90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="I90" s="64" t="s">
-        <v>72</v>
-      </c>
-      <c r="J90" s="64"/>
-      <c r="K90" s="64"/>
-      <c r="L90" s="64"/>
-      <c r="M90" s="64"/>
+      <c r="D90" s="65"/>
+      <c r="E90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="G90" s="68"/>
+      <c r="H90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="I90" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="J90" s="65"/>
+      <c r="K90" s="65"/>
+      <c r="L90" s="65"/>
+      <c r="M90" s="65"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M90" xr:uid="{C6D2D344-3C1F-449C-B697-53FB90F953F5}"/>

--- a/file/Catalog_Experiences_Web_VPATJ03600.xlsx
+++ b/file/Catalog_Experiences_Web_VPATJ03600.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C76B3DE-D230-41C4-B92E-94BB49D9E632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{12A8C8D7-8198-4E2E-80F9-486F1BBC83D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{6BDCFBF7-A53C-477F-9FB0-3BC33E5182F9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{B0EDEDD9-B90E-41E8-82EB-A3D695399800}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2026</t>
+      <t>2025</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>12</t>
+      <t>14</t>
     </r>
     <r>
       <rPr>
@@ -192,7 +192,6 @@
   </si>
   <si>
     <t>Catalog Experiences(Web)</t>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -270,7 +269,6 @@
       </rPr>
       <t>エコシステム向けのカタログ体験を提供する製品です。</t>
     </r>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <r>
@@ -1706,7 +1704,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2626,8 +2624,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428CA5AB-75FE-4778-A6B8-58BB6923C1D8}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF68F8-6FDB-4892-BD73-CD6C48786DEF}">
+  <sheetPr codeName="Sheet231">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -3445,7 +3443,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D155A5FE-C25E-4853-BD44-CEF726E85B7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6339150C-3443-4FB1-9988-696572A079AD}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Catalog_Experiences_Web_VPATJ03600.xlsx
+++ b/file/Catalog_Experiences_Web_VPATJ03600.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12A8C8D7-8198-4E2E-80F9-486F1BBC83D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9412A0B-1871-45A6-953C-BDA983522726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{B0EDEDD9-B90E-41E8-82EB-A3D695399800}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{751996E5-3398-4A03-A416-530F670DAA73}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,833 +38,197 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="234">
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービスのアクセシビリティ自己評価様式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>作成日：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品画像</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>企業・団体名</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>日本マイクロソフト株式会社</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
+  <si>
+    <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
+  </si>
+  <si>
+    <t>作成日：2026年8月12日</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品画像</t>
+  </si>
+  <si>
+    <t>企業・団体名</t>
+  </si>
+  <si>
+    <t>日本マイクロソフト株式会社</t>
     <rPh sb="0" eb="2">
       <t>ニホン</t>
     </rPh>
     <rPh sb="9" eb="13">
       <t>カブシキガイシャ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Catalog Experiences
 (Web)</t>
   </si>
   <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス名称</t>
-    </r>
+    <t>ICT機器・サービス名称</t>
   </si>
   <si>
     <t>Catalog Experiences(Web)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>型番</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>ICT</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機器・サービス概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Catalog Experiences(Web)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dataverse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>および</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Power Platform</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>エコシステム向けのカタログ体験を提供する製品です。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>問合せ先</t>
-    </r>
+    <t>型番</t>
+  </si>
+  <si>
+    <t>ICT機器・サービス概要</t>
+  </si>
+  <si>
+    <t>Catalog Experiences(Web)は、DataverseおよびPower Platformエコシステム向けのカタログ体験を提供する製品です。</t>
+  </si>
+  <si>
+    <t>問合せ先</t>
   </si>
   <si>
     <t>0120-167-400</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ウェブサイト</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>URL</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>機能性能</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>配慮対象アクセス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価結果</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>視力なしでの使用（全盲）</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた視力での使用（弱視、ロービジョン）</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>色知覚なしでの使用</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>評価不要</t>
-    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウェブサイトURL</t>
+  </si>
+  <si>
+    <t>機能性能</t>
+  </si>
+  <si>
+    <t>配慮対象アクセス</t>
+  </si>
+  <si>
+    <t>評価結果</t>
+  </si>
+  <si>
+    <t>概要</t>
+  </si>
+  <si>
+    <t>視力なしでの使用（全盲）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対応している</t>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、視力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた視力での使用（弱視、ロービジョン）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>色知覚なしでの使用</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>評価不要</t>
     <rPh sb="0" eb="4">
       <t>ヒョウカフヨウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条を用いているため評価の対象外である。</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた聴力での使用（難聴）</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>発話能力なしでの使用</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条を用いているため評価の対象外である。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>聴力なしでの使用（全ろう）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた聴力での使用（難聴）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+  </si>
+  <si>
+    <t>発話能力なしでの使用</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対応している</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>光の点滅による影響の最小化（光感受性発作）</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>対応している</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>すべての製品において要件を満たす。</t>
-    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた器用さ又は力での使用</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>限られた手の届く範囲での使用</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>光の点滅による影響の最小化（光感受性発作）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対応している</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>すべての製品において要件を満たす。</t>
     <rPh sb="4" eb="6">
       <t>セイヒン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>プライバシー</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>サポート対応　概要</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>ドキュメントとサポートサービス</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>FAX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等）が提供されているか。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>用いた技術基準</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>米国リハビリテーション法</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>508</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>条</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>免責事項</t>
-    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
+  </si>
+  <si>
+    <t>プライバシー</t>
+  </si>
+  <si>
+    <t>製品・サービスがアクセシビリティ機能を提供する場合、アクセシビリティ機能を使用するにあたりプライバシーが守られる操作モードが用意されているか</t>
+  </si>
+  <si>
+    <t>サポート対応　概要</t>
+  </si>
+  <si>
+    <t>ドキュメントとサポートサービス</t>
+  </si>
+  <si>
+    <t>製品の取扱説明書や問合せ先が提供されているか。また、アクセシビリティに配慮したサポート（取扱説明書、電話や手話（筆記）窓口、FAX等）が提供されているか。</t>
+  </si>
+  <si>
+    <t>用いた技術基準</t>
+  </si>
+  <si>
+    <t>米国リハビリテーション法508条</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>免責事項</t>
   </si>
   <si>
     <t>章・項・節</t>
@@ -877,18 +241,18 @@
     <rPh sb="4" eb="5">
       <t>セツ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Provision Title</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
       <t>コウモクメイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>規格内容</t>
@@ -898,84 +262,48 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>視力なしでの使用（全盲）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>限られた視力での使用（弱視、ロービジョン）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>色知覚なしでの使用</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>聴力なしでの使用（全ろう）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>限られた聴力での使用（難聴）</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>発話能力なしでの使用</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>限られた器用さ又は力での使用</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>限られた手の届く範囲での使用</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>光の点滅による影響の最小化（光感受性発作）</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>General</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>●</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Functional Performance Criteria</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>機能的性能基準</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Without Vision</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>視力なし</t>
     <rPh sb="0" eb="2">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>●</t>
   </si>
   <si>
     <t>With Limited Vision</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>限られた視力</t>
@@ -985,11 +313,11 @@
     <rPh sb="4" eb="6">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Without Perception of Color</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>色彩感覚なし</t>
@@ -999,22 +327,22 @@
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> Without Hearing</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>聴力なし</t>
     <rPh sb="0" eb="2">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>With Limited Hearing</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>限られた聴力</t>
@@ -1024,22 +352,22 @@
     <rPh sb="4" eb="6">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Without Speech</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>発話能力なし</t>
     <rPh sb="0" eb="4">
       <t>ハツワノウリョク</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Manipulation</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>限定的な操作</t>
@@ -1049,11 +377,11 @@
     <rPh sb="4" eb="6">
       <t>ソウサ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Reach and Strength</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>限られた手の届く範囲と力の強さ</t>
@@ -1063,138 +391,138 @@
     <rPh sb="13" eb="14">
       <t>ツヨ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Language, Cognitive, and Learning Abilities</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>限られた言語能力、認知能力、学習能力</t>
     <rPh sb="0" eb="1">
       <t>カギ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Closed Functionality</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>クローズドな機能</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Speech-Output Enabled</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>音声出力可能</t>
   </si>
   <si>
     <t>402.2.1</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> Information Displayed On-Screen</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> 画面に表示される情報</t>
   </si>
   <si>
     <t>402.2.2</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Transactional Outputs</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>トランザクション出力</t>
   </si>
   <si>
     <t>402.2.3</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Speech Delivery Type and Coordination</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>音声配信の種類と連携</t>
   </si>
   <si>
     <t>402.2.4</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>User Control</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ユーザーコントロール</t>
   </si>
   <si>
     <t>402.2.5</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Braille Instructions</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> 点字説明</t>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>402.3.1</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Private Listening</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>個人的な聞き取り</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>402.3.2</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Non-Private Listening</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>非個人的な聞き取り</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve">Characters on Display Screens
 </t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ディスプレイ上の文字</t>
   </si>
   <si>
     <t>Characters on Variable Message Signs</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>可変メッセージ看板の文字</t>
   </si>
   <si>
     <t>Biometrics</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>バイオメトリクス</t>
@@ -1207,88 +535,88 @@
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>アクセシビリティのための情報の保存</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>一般</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Privacy</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>個人情報保護</t>
   </si>
   <si>
     <t>Standard Connections</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>標準接続</t>
   </si>
   <si>
     <t>Operable Parts</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>操作可能な部品</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrast</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> コントラスト</t>
   </si>
   <si>
     <t xml:space="preserve"> Input Controls (and sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> 入力コントロール（およびその下位規定）</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> Key Repeat</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>キーリピート</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Timed Response</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>時限反応</t>
   </si>
   <si>
     <t>Operation</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>操作方法</t>
   </si>
   <si>
     <t xml:space="preserve"> Keys, Tickets, and Fare Cards</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> キー、チケット、料金カード</t>
     <rPh sb="9" eb="11">
       <t>リョウキン</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Reach Height (and sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>届く高さ（およびその下位規定）</t>
@@ -1298,32 +626,32 @@
     <rPh sb="2" eb="3">
       <t>タカ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Display Screens</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>表示画面</t>
   </si>
   <si>
     <t>Visibility</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>視認性</t>
   </si>
   <si>
     <t>Flashing</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>点滅表示</t>
   </si>
   <si>
     <t>Status Indicators</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>状態表示</t>
@@ -1333,88 +661,88 @@
     <rPh sb="2" eb="4">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Color Coding</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>カラーコード</t>
   </si>
   <si>
     <t>Audible Signals</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>可聴信号</t>
   </si>
   <si>
     <t>ICT With Two-Way Voice Communication</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>双方向音声通話機能付きICT</t>
   </si>
   <si>
     <t xml:space="preserve"> Volume Gain</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> ボリュームゲイン</t>
   </si>
   <si>
     <t>Interference Reduction and Magnetic Coupling (and sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>妨害波低減と磁気結合（およびその下位規定）</t>
   </si>
   <si>
     <t>Digitally Encoded Speech</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>デジタル符号化音声</t>
   </si>
   <si>
     <t xml:space="preserve"> Real-Time Text Functionality (Reserved)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> リアルタイムテキスト機能(予約)</t>
   </si>
   <si>
     <t xml:space="preserve"> Caller ID</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> 発信者番号通知</t>
   </si>
   <si>
     <t>Video Communication</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ビデオ通信</t>
   </si>
   <si>
     <t>Caption Processing Technologies</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>キャプション処理技術</t>
   </si>
   <si>
     <t>General (includes sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>一般（下位規定含む）</t>
   </si>
   <si>
     <t>Audio Description Processing Technology</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>音声説明処理技術</t>
@@ -1424,28 +752,28 @@
   </si>
   <si>
     <t>User Controls for Captions and Audio Description</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>字幕・音声説明のユーザー制御技術</t>
   </si>
   <si>
     <t>General (and sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>一般（および下位規定）</t>
   </si>
   <si>
     <t>Interoperability With Assistive Technology</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>支援技術との相互運用性</t>
   </si>
   <si>
     <t>Accessibility Services (and sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>アクセシビリティサービス（および下位規定）</t>
@@ -1455,164 +783,164 @@
   </si>
   <si>
     <t>Platform Accessibility Features</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>プラットフォームアクセシビリティ機能</t>
   </si>
   <si>
     <t>A. Section 9.3.3</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Enable sequential entry of multiple (chorded) keystrokes</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>複数のキーストロークを連続して入力できる</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>B. Section 9.3.4</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Provide adjustment of delay before key acceptance</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>キー受理までの遅延時間の調整</t>
   </si>
   <si>
     <t>C. Section 9.3.5</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Provide adjustment of same-key double-strike acceptance</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>同じキーの連打を受け入れるかどうかを調整できるようにした</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>D. Section 10.6.7</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Allow users to choose visual alternative for audio output</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>音声出力に代わる視覚的な選択肢をユーザーが選択可能</t>
   </si>
   <si>
     <t>E. Section 10.6.8</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> Synchronize audio equivalents for visual events</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> 視覚的イベントと音声を同期させる</t>
   </si>
   <si>
     <t>F. Section 10.6.9</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Provide speech output services</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>音声出力サービスの提供</t>
   </si>
   <si>
     <t>G. Section 10.7.1</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Display any captions provided</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>提供されたキャプションの表示</t>
   </si>
   <si>
     <t>Applications</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>アプリケーション</t>
   </si>
   <si>
     <t xml:space="preserve"> User Preferences</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> ユーザー設定</t>
   </si>
   <si>
     <t>Alternative User Interfaces</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>代替ユーザーインターフェイス</t>
   </si>
   <si>
     <t>User Controls for Captions and Audio Description (includes sub-provisions)</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>キャプションとオーディオディスクリプションのためのユーザーコントロール（下位規定を含む）</t>
   </si>
   <si>
     <t>Authoring Tools</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>オーサリングツール</t>
   </si>
   <si>
     <t xml:space="preserve"> Content Creation or Editing</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t xml:space="preserve"> コンテンツの作成または編集</t>
   </si>
   <si>
     <t>504.2.1</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility in Format Conversion</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>フォーマット変換におけるアクセシビリティのための情報提供の保存</t>
   </si>
   <si>
     <t>504.2.2</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PDF Export</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PDFの書き出し</t>
   </si>
   <si>
     <t>Prompts</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>プロンプト</t>
   </si>
   <si>
     <t>Templates</t>
-    <phoneticPr fontId="3"/>
+    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>テンプレート</t>
@@ -1622,7 +950,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1630,13 +958,6 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1654,37 +975,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1696,26 +997,14 @@
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
+      <sz val="28"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="36"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
+      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -1731,16 +1020,33 @@
     </font>
     <font>
       <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10.5"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <b/>
@@ -2066,7 +1372,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2077,184 +1383,184 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -2278,16 +1584,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2624,228 +1930,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAF68F8-6FDB-4892-BD73-CD6C48786DEF}">
-  <sheetPr codeName="Sheet231">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3F5C7D-88A1-4AA2-A4FF-70DEE7FA2D8B}">
+  <sheetPr codeName="Sheet250">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
   <sheetFormatPr defaultColWidth="8.58203125" defaultRowHeight="14.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="20.08203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.58203125" style="3" customWidth="1"/>
-    <col min="5" max="7" width="9.08203125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="8.58203125" style="3"/>
-    <col min="9" max="9" width="28.33203125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="8.58203125" style="3"/>
+    <col min="1" max="1" width="20.08203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.08203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.58203125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="9.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" style="2"/>
+    <col min="9" max="9" width="28.33203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="11" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="19"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="2"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24"/>
       <c r="I14" s="25"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
@@ -3189,28 +2495,28 @@
       <c r="I39" s="42"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
@@ -3260,15 +2566,15 @@
       <c r="I44" s="42"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
@@ -3287,11 +2593,11 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="55"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="5"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="56"/>
       <c r="H47" s="56"/>
       <c r="I47" s="57"/>
@@ -3436,14 +2742,14 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6339150C-3443-4FB1-9988-696572A079AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30527996-333C-4333-B66F-B1470C5299DC}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3468,31 +2774,31 @@
         <v>55</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3500,36 +2806,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3537,10 +2843,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3558,14 +2864,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3581,15 +2887,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3604,15 +2910,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3627,17 +2933,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3650,10 +2956,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3661,7 +2967,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3673,10 +2979,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3685,7 +2991,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3696,10 +3002,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3709,10 +3015,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3721,10 +3027,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3734,10 +3040,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3746,10 +3052,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3767,17 +3073,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3792,10 +3098,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3813,10 +3119,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3831,17 +3137,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3854,17 +3160,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3877,20 +3183,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3902,20 +3208,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3927,17 +3233,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3953,10 +3259,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3964,7 +3270,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3973,23 +3279,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3998,23 +3304,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4026,15 +3332,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4049,15 +3355,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4072,27 +3378,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4101,10 +3407,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4122,29 +3428,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4153,10 +3459,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4174,17 +3480,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4199,10 +3505,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4220,30 +3526,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4251,10 +3557,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4272,31 +3578,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4305,10 +3611,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4326,15 +3632,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4349,14 +3655,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4372,10 +3678,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4385,10 +3691,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4397,27 +3703,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4426,10 +3732,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4439,10 +3745,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4451,14 +3757,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4474,10 +3780,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4487,10 +3793,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4499,10 +3805,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4512,10 +3818,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4524,10 +3830,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4545,10 +3851,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4566,10 +3872,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4587,14 +3893,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4610,10 +3916,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4631,15 +3937,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4654,10 +3960,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4675,20 +3981,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4700,10 +4006,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4721,29 +4027,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4752,10 +4058,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4773,10 +4079,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4784,7 +4090,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4796,10 +4102,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4807,7 +4113,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4819,10 +4125,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4830,7 +4136,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4842,10 +4148,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4863,24 +4169,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4892,17 +4198,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4915,20 +4221,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4940,10 +4246,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4961,14 +4267,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4984,10 +4290,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -5005,22 +4311,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5032,10 +4338,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5053,31 +4359,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5086,10 +4392,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5107,29 +4413,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5138,14 +4444,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5153,10 +4459,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5165,43 +4471,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5211,22 +4517,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5236,22 +4542,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5261,32 +4567,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5295,23 +4601,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5320,26 +4626,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5347,23 +4653,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5375,31 +4681,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5408,10 +4714,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5429,15 +4735,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5452,14 +4758,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5467,10 +4773,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5479,22 +4785,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5506,24 +4812,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5535,10 +4841,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5556,24 +4862,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5582,25 +4888,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5609,20 +4915,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5637,24 +4943,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5666,24 +4972,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
@@ -5857,7 +5163,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/file/Catalog_Experiences_Web_VPATJ03600.xlsx
+++ b/file/Catalog_Experiences_Web_VPATJ03600.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9412A0B-1871-45A6-953C-BDA983522726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E41EFAF-197B-41E4-9157-C7A6F7257D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{751996E5-3398-4A03-A416-530F670DAA73}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{F803E7E0-6AB1-4B84-8E05-08A8188EA8A3}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年8月12日</t>
+    <t>作成日：2025年8月14日</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -1930,8 +1930,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3F5C7D-88A1-4AA2-A4FF-70DEE7FA2D8B}">
-  <sheetPr codeName="Sheet250">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2838D0EE-42A5-411B-9EAD-8E0986F68BD5}">
+  <sheetPr codeName="Sheet247">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2749,7 +2749,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30527996-333C-4333-B66F-B1470C5299DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28730BD-4C58-469E-A2F5-6C299C91ADE7}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Catalog_Experiences_Web_VPATJ03600.xlsx
+++ b/file/Catalog_Experiences_Web_VPATJ03600.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E41EFAF-197B-41E4-9157-C7A6F7257D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA975725-A1DC-4B21-BED9-3379CD1F8DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{F803E7E0-6AB1-4B84-8E05-08A8188EA8A3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{558D35DF-25F1-4201-9D08-0A0CBA4A83D8}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,13 +38,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="226">
   <si>
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2025年8月14日</t>
-    <phoneticPr fontId="2"/>
+    <t>作成日：2026年8月12日</t>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品画像</t>
@@ -60,7 +60,7 @@
     <rPh sb="9" eb="13">
       <t>カブシキガイシャ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Catalog Experiences
@@ -86,12 +86,15 @@
   </si>
   <si>
     <t>0120-167-400</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ウェブサイトURL</t>
   </si>
   <si>
+    <t>https://www.microsoft.com/en-us/power-platform/products/catalog-experiences</t>
+  </si>
+  <si>
     <t>機能性能</t>
   </si>
   <si>
@@ -105,7 +108,7 @@
   </si>
   <si>
     <t>視力なしでの使用（全盲）</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>対応している</t>
@@ -118,89 +121,89 @@
   </si>
   <si>
     <t>限られた視力での使用（弱視、ロービジョン）</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが視覚的な操作モードで提供される場合、限られた視力で対応可能な操作モードが用意されているか</t>
   </si>
   <si>
     <t>色知覚なしでの使用</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>評価不要</t>
     <rPh sb="0" eb="4">
       <t>ヒョウカフヨウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>米国リハビリテーション法508条を用いているため評価の対象外である。</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
   </si>
   <si>
     <t>聴力なしでの使用（全ろう）</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
   </si>
   <si>
     <t>限られた聴力での使用（難聴）</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
   </si>
   <si>
     <t>発話能力なしでの使用</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>対応している</t>
     <rPh sb="0" eb="2">
       <t>タイオウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>すべての製品において要件を満たす。</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
   </si>
   <si>
     <t>限られた器用さ又は力での使用</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
   </si>
   <si>
     <t>限られた手の届く範囲での使用</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
   </si>
   <si>
     <t>光の点滅による影響の最小化（光感受性発作）</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>対応している</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>すべての製品において要件を満たす。</t>
     <rPh sb="4" eb="6">
       <t>セイヒン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>製品が視覚的な操作モードで提供される場合、光感受性発作を引き起こすリスクを最小化するような配慮がなされているか</t>
@@ -225,7 +228,7 @@
   </si>
   <si>
     <t>米国リハビリテーション法508条</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>免責事項</t>
@@ -241,18 +244,18 @@
     <rPh sb="4" eb="5">
       <t>セツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provision Title</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>項目名</t>
     <rPh sb="0" eb="3">
       <t>コウモクメイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>規格内容</t>
@@ -262,48 +265,48 @@
     <rPh sb="2" eb="4">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>General</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Functional Performance Criteria</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>機能的性能基準</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Vision</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視力なし</t>
     <rPh sb="0" eb="2">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>●</t>
   </si>
   <si>
     <t>With Limited Vision</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた視力</t>
@@ -313,11 +316,11 @@
     <rPh sb="4" eb="6">
       <t>シリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Perception of Color</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>色彩感覚なし</t>
@@ -327,22 +330,22 @@
     <rPh sb="2" eb="4">
       <t>カンカク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Without Hearing</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>聴力なし</t>
     <rPh sb="0" eb="2">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>With Limited Hearing</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた聴力</t>
@@ -352,22 +355,22 @@
     <rPh sb="4" eb="6">
       <t>チョウリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Without Speech</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>発話能力なし</t>
     <rPh sb="0" eb="4">
       <t>ハツワノウリョク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Manipulation</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限定的な操作</t>
@@ -377,11 +380,11 @@
     <rPh sb="4" eb="6">
       <t>ソウサ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Reach and Strength</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた手の届く範囲と力の強さ</t>
@@ -391,138 +394,138 @@
     <rPh sb="13" eb="14">
       <t>ツヨ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> With Limited Language, Cognitive, and Learning Abilities</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>限られた言語能力、認知能力、学習能力</t>
     <rPh sb="0" eb="1">
       <t>カギ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Closed Functionality</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>クローズドな機能</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech-Output Enabled</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力可能</t>
   </si>
   <si>
     <t>402.2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Information Displayed On-Screen</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 画面に表示される情報</t>
   </si>
   <si>
     <t>402.2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Transactional Outputs</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>トランザクション出力</t>
   </si>
   <si>
     <t>402.2.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Speech Delivery Type and Coordination</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声配信の種類と連携</t>
   </si>
   <si>
     <t>402.2.4</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>User Control</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ユーザーコントロール</t>
   </si>
   <si>
     <t>402.2.5</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Braille Instructions</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 点字説明</t>
   </si>
   <si>
     <t>Volume</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音量</t>
   </si>
   <si>
     <t>402.3.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Private Listening</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人的な聞き取り</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>402.3.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Non-Private Listening</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>非個人的な聞き取り</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">Characters on Display Screens
 </t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ディスプレイ上の文字</t>
   </si>
   <si>
     <t>Characters on Variable Message Signs</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可変メッセージ看板の文字</t>
   </si>
   <si>
     <t>Biometrics</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>バイオメトリクス</t>
@@ -535,88 +538,88 @@
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティのための情報の保存</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Privacy</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>個人情報保護</t>
   </si>
   <si>
     <t>Standard Connections</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>標準接続</t>
   </si>
   <si>
     <t>Operable Parts</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作可能な部品</t>
   </si>
   <si>
     <t xml:space="preserve"> Contrast</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コントラスト</t>
   </si>
   <si>
     <t xml:space="preserve"> Input Controls (and sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 入力コントロール（およびその下位規定）</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Key Repeat</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キーリピート</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Timed Response</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>時限反応</t>
   </si>
   <si>
     <t>Operation</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>操作方法</t>
   </si>
   <si>
     <t xml:space="preserve"> Keys, Tickets, and Fare Cards</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> キー、チケット、料金カード</t>
     <rPh sb="9" eb="11">
       <t>リョウキン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Reach Height (and sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>届く高さ（およびその下位規定）</t>
@@ -626,32 +629,32 @@
     <rPh sb="2" eb="3">
       <t>タカ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display Screens</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>表示画面</t>
   </si>
   <si>
     <t>Visibility</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>視認性</t>
   </si>
   <si>
     <t>Flashing</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>点滅表示</t>
   </si>
   <si>
     <t>Status Indicators</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>状態表示</t>
@@ -661,88 +664,88 @@
     <rPh sb="2" eb="4">
       <t>ヒョウジ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Color Coding</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>カラーコード</t>
   </si>
   <si>
     <t>Audible Signals</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>可聴信号</t>
   </si>
   <si>
     <t>ICT With Two-Way Voice Communication</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>双方向音声通話機能付きICT</t>
   </si>
   <si>
     <t xml:space="preserve"> Volume Gain</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ボリュームゲイン</t>
   </si>
   <si>
     <t>Interference Reduction and Magnetic Coupling (and sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>妨害波低減と磁気結合（およびその下位規定）</t>
   </si>
   <si>
     <t>Digitally Encoded Speech</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>デジタル符号化音声</t>
   </si>
   <si>
     <t xml:space="preserve"> Real-Time Text Functionality (Reserved)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> リアルタイムテキスト機能(予約)</t>
   </si>
   <si>
     <t xml:space="preserve"> Caller ID</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 発信者番号通知</t>
   </si>
   <si>
     <t>Video Communication</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>ビデオ通信</t>
   </si>
   <si>
     <t>Caption Processing Technologies</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプション処理技術</t>
   </si>
   <si>
     <t>General (includes sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（下位規定含む）</t>
   </si>
   <si>
     <t>Audio Description Processing Technology</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声説明処理技術</t>
@@ -752,28 +755,28 @@
   </si>
   <si>
     <t>User Controls for Captions and Audio Description</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>字幕・音声説明のユーザー制御技術</t>
   </si>
   <si>
     <t>General (and sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>一般（および下位規定）</t>
   </si>
   <si>
     <t>Interoperability With Assistive Technology</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>支援技術との相互運用性</t>
   </si>
   <si>
     <t>Accessibility Services (and sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アクセシビリティサービス（および下位規定）</t>
@@ -783,164 +786,164 @@
   </si>
   <si>
     <t>Platform Accessibility Features</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プラットフォームアクセシビリティ機能</t>
   </si>
   <si>
     <t>A. Section 9.3.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Enable sequential entry of multiple (chorded) keystrokes</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>複数のキーストロークを連続して入力できる</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>B. Section 9.3.4</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of delay before key acceptance</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キー受理までの遅延時間の調整</t>
   </si>
   <si>
     <t>C. Section 9.3.5</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide adjustment of same-key double-strike acceptance</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>同じキーの連打を受け入れるかどうかを調整できるようにした</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>D. Section 10.6.7</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Allow users to choose visual alternative for audio output</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力に代わる視覚的な選択肢をユーザーが選択可能</t>
   </si>
   <si>
     <t>E. Section 10.6.8</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> Synchronize audio equivalents for visual events</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> 視覚的イベントと音声を同期させる</t>
   </si>
   <si>
     <t>F. Section 10.6.9</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Provide speech output services</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>音声出力サービスの提供</t>
   </si>
   <si>
     <t>G. Section 10.7.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Display any captions provided</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>提供されたキャプションの表示</t>
   </si>
   <si>
     <t>Applications</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>アプリケーション</t>
   </si>
   <si>
     <t xml:space="preserve"> User Preferences</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> ユーザー設定</t>
   </si>
   <si>
     <t>Alternative User Interfaces</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>代替ユーザーインターフェイス</t>
   </si>
   <si>
     <t>User Controls for Captions and Audio Description (includes sub-provisions)</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>キャプションとオーディオディスクリプションのためのユーザーコントロール（下位規定を含む）</t>
   </si>
   <si>
     <t>Authoring Tools</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>オーサリングツール</t>
   </si>
   <si>
     <t xml:space="preserve"> Content Creation or Editing</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve"> コンテンツの作成または編集</t>
   </si>
   <si>
     <t>504.2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Preservation of Information Provided for Accessibility in Format Conversion</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>フォーマット変換におけるアクセシビリティのための情報提供の保存</t>
   </si>
   <si>
     <t>504.2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDF Export</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PDFの書き出し</t>
   </si>
   <si>
     <t>Prompts</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>プロンプト</t>
   </si>
   <si>
     <t>Templates</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>テンプレート</t>
@@ -954,6 +957,15 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -1008,15 +1020,6 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1372,7 +1375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1380,175 +1383,175 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1930,8 +1933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2838D0EE-42A5-411B-9EAD-8E0986F68BD5}">
-  <sheetPr codeName="Sheet247">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D5EADDA-498D-4BEE-AF71-31FD738B108D}">
+  <sheetPr codeName="Sheet253">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2120,7 +2123,9 @@
       <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="22"/>
+      <c r="B14" s="22" t="s">
+        <v>14</v>
+      </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="9"/>
@@ -2142,7 +2147,7 @@
     </row>
     <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2155,15 +2160,15 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
       <c r="D17" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
@@ -2172,15 +2177,15 @@
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="33"/>
       <c r="C18" s="34"/>
       <c r="D18" s="35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
@@ -2189,7 +2194,7 @@
     </row>
     <row r="19" spans="1:9" ht="50.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" s="40"/>
       <c r="C19" s="41"/>
@@ -2202,15 +2207,15 @@
     </row>
     <row r="20" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" s="33"/>
       <c r="C20" s="34"/>
       <c r="D20" s="46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
@@ -2219,7 +2224,7 @@
     </row>
     <row r="21" spans="1:9" ht="44.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="40"/>
       <c r="C21" s="41"/>
@@ -2232,15 +2237,15 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="33"/>
       <c r="C22" s="34"/>
       <c r="D22" s="42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F22" s="42"/>
       <c r="G22" s="42"/>
@@ -2249,7 +2254,7 @@
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
@@ -2262,15 +2267,15 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
       <c r="D24" s="35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F24" s="37"/>
       <c r="G24" s="37"/>
@@ -2279,7 +2284,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2292,15 +2297,15 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
       <c r="D26" s="35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="37"/>
       <c r="G26" s="37"/>
@@ -2309,7 +2314,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -2322,15 +2327,15 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" s="42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F28" s="42"/>
       <c r="G28" s="42"/>
@@ -2339,7 +2344,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -2352,15 +2357,15 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
       <c r="D30" s="46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
@@ -2369,7 +2374,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -2382,7 +2387,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -2395,7 +2400,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -2408,15 +2413,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -2425,7 +2430,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -2449,15 +2454,15 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B37" s="28"/>
       <c r="C37" s="29"/>
       <c r="D37" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
@@ -2466,15 +2471,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -2483,7 +2488,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -2507,7 +2512,7 @@
     </row>
     <row r="41" spans="1:9" ht="16.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -2520,15 +2525,15 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="29"/>
       <c r="D42" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F42" s="31"/>
       <c r="G42" s="31"/>
@@ -2537,15 +2542,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -2554,7 +2559,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -2578,10 +2583,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -2604,7 +2609,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -2742,14 +2747,17 @@
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B14:E14"/>
   </mergeCells>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
+  <hyperlinks>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{DB984C1E-79C0-483C-9127-139F485ED213}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28730BD-4C58-469E-A2F5-6C299C91ADE7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70D63515-A2D5-4648-AF6B-CD87AE067C72}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -2762,43 +2770,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2806,36 +2814,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -2843,10 +2851,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -2864,14 +2872,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -2887,15 +2895,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -2910,15 +2918,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -2933,17 +2941,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -2956,10 +2964,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -2967,7 +2975,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -2979,10 +2987,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -2991,7 +2999,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3002,10 +3010,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3015,10 +3023,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3027,10 +3035,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3040,10 +3048,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3052,10 +3060,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3073,17 +3081,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3098,10 +3106,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3119,10 +3127,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3137,17 +3145,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3160,17 +3168,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3183,20 +3191,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3208,20 +3216,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3233,17 +3241,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3259,10 +3267,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3270,7 +3278,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3279,23 +3287,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3304,23 +3312,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3332,15 +3340,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -3355,15 +3363,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -3378,27 +3386,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -3407,10 +3415,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -3428,29 +3436,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -3459,10 +3467,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -3480,17 +3488,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -3505,10 +3513,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -3526,30 +3534,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3557,10 +3565,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -3578,31 +3586,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -3611,10 +3619,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -3632,15 +3640,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -3655,14 +3663,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -3678,10 +3686,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -3691,10 +3699,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -3703,27 +3711,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -3732,10 +3740,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -3745,10 +3753,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -3757,14 +3765,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -3780,10 +3788,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -3793,10 +3801,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -3805,10 +3813,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -3818,10 +3826,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -3830,10 +3838,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -3851,10 +3859,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -3872,10 +3880,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -3893,14 +3901,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -3916,10 +3924,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -3937,15 +3945,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -3960,10 +3968,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -3981,20 +3989,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4006,10 +4014,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4027,29 +4035,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4058,10 +4066,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4079,10 +4087,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4090,7 +4098,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4102,10 +4110,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4113,7 +4121,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4125,10 +4133,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4136,7 +4144,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4148,10 +4156,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4169,24 +4177,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4198,17 +4206,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4221,20 +4229,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4246,10 +4254,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4267,14 +4275,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4290,10 +4298,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4311,22 +4319,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4338,10 +4346,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -4359,31 +4367,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -4392,10 +4400,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -4413,29 +4421,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -4444,14 +4452,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -4459,10 +4467,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -4471,43 +4479,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -4517,22 +4525,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -4542,22 +4550,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -4567,32 +4575,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -4601,23 +4609,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -4626,26 +4634,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -4653,23 +4661,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -4681,31 +4689,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -4714,10 +4722,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -4735,15 +4743,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -4758,14 +4766,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -4773,10 +4781,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -4785,22 +4793,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -4812,24 +4820,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -4841,10 +4849,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -4862,24 +4870,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -4888,25 +4896,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -4915,20 +4923,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -4943,24 +4951,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -4972,24 +4980,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>
@@ -5163,7 +5171,7 @@
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:J3"/>
   </mergeCells>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
